--- a/AAII_Financials/Quarterly/CLRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CLRI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>CLRI</t>
   </si>
@@ -656,136 +656,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -793,10 +800,10 @@
         <v>600</v>
       </c>
       <c r="E8" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F8" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G8" s="3">
         <v>500</v>
@@ -811,10 +818,10 @@
         <v>500</v>
       </c>
       <c r="K8" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L8" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M8" s="3">
         <v>400</v>
@@ -829,13 +836,13 @@
         <v>400</v>
       </c>
       <c r="Q8" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="R8" s="3">
         <v>400</v>
       </c>
       <c r="S8" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="T8" s="3">
         <v>400</v>
@@ -844,37 +851,43 @@
         <v>300</v>
       </c>
       <c r="V8" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="W8" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X8" s="3">
         <v>200</v>
       </c>
       <c r="Y8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z8" s="3">
         <v>200</v>
       </c>
       <c r="AA8" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC8" s="3">
         <v>300</v>
       </c>
-      <c r="AB8" s="3">
-        <v>200</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>200</v>
-      </c>
       <c r="AD8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE8" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -930,25 +943,25 @@
         <v>100</v>
       </c>
       <c r="U9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W9" s="3">
+        <v>0</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
         <v>-100</v>
       </c>
-      <c r="X9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>0</v>
-      </c>
       <c r="Z9" s="3">
         <v>0</v>
       </c>
       <c r="AA9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="3">
         <v>0</v>
@@ -960,10 +973,16 @@
         <v>0</v>
       </c>
       <c r="AE9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -971,10 +990,10 @@
         <v>500</v>
       </c>
       <c r="E10" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F10" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G10" s="3">
         <v>400</v>
@@ -989,10 +1008,10 @@
         <v>400</v>
       </c>
       <c r="K10" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L10" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M10" s="3">
         <v>300</v>
@@ -1007,25 +1026,25 @@
         <v>300</v>
       </c>
       <c r="Q10" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="R10" s="3">
         <v>300</v>
       </c>
       <c r="S10" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="T10" s="3">
         <v>300</v>
       </c>
       <c r="U10" s="3">
+        <v>200</v>
+      </c>
+      <c r="V10" s="3">
         <v>300</v>
       </c>
-      <c r="V10" s="3">
-        <v>200</v>
-      </c>
       <c r="W10" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X10" s="3">
         <v>200</v>
@@ -1043,16 +1062,22 @@
         <v>200</v>
       </c>
       <c r="AC10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AE10" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1109,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1099,13 +1126,13 @@
         <v>0</v>
       </c>
       <c r="G12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3">
         <v>0</v>
       </c>
       <c r="I12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -1132,40 +1159,40 @@
         <v>0</v>
       </c>
       <c r="R12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S12" s="3">
         <v>0</v>
       </c>
       <c r="T12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W12" s="3">
         <v>100</v>
       </c>
       <c r="X12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y12" s="3">
         <v>100</v>
       </c>
       <c r="Z12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="3">
         <v>100</v>
       </c>
       <c r="AB12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD12" s="3">
         <v>0</v>
@@ -1173,8 +1200,14 @@
       <c r="AE12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1262,43 +1295,49 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>10</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>10</v>
@@ -1312,47 +1351,53 @@
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>10</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="3">
-        <v>200</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC14" s="3">
         <v>200</v>
       </c>
       <c r="AD14" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1389,17 +1434,17 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P15" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1426,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="AA15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1438,10 +1483,16 @@
         <v>0</v>
       </c>
       <c r="AE15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,8 +1521,10 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1479,49 +1532,49 @@
         <v>600</v>
       </c>
       <c r="E17" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F17" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G17" s="3">
         <v>400</v>
       </c>
       <c r="H17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I17" s="3">
         <v>400</v>
       </c>
       <c r="J17" s="3">
+        <v>400</v>
+      </c>
+      <c r="K17" s="3">
+        <v>400</v>
+      </c>
+      <c r="L17" s="3">
         <v>500</v>
       </c>
-      <c r="K17" s="3">
-        <v>200</v>
-      </c>
-      <c r="L17" s="3">
-        <v>300</v>
-      </c>
       <c r="M17" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="N17" s="3">
         <v>300</v>
       </c>
       <c r="O17" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="P17" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Q17" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="R17" s="3">
         <v>400</v>
       </c>
       <c r="S17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="T17" s="3">
         <v>400</v>
@@ -1530,37 +1583,43 @@
         <v>400</v>
       </c>
       <c r="V17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W17" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="X17" s="3">
         <v>300</v>
       </c>
       <c r="Y17" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Z17" s="3">
         <v>300</v>
       </c>
       <c r="AA17" s="3">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="AB17" s="3">
         <v>300</v>
       </c>
       <c r="AC17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE17" s="3">
         <v>800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1568,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
         <v>0</v>
@@ -1577,40 +1636,40 @@
         <v>100</v>
       </c>
       <c r="H18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3">
         <v>100</v>
       </c>
       <c r="J18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M18" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N18" s="3">
         <v>100</v>
       </c>
       <c r="O18" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R18" s="3">
         <v>0</v>
       </c>
       <c r="S18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T18" s="3">
         <v>0</v>
@@ -1619,7 +1678,7 @@
         <v>-100</v>
       </c>
       <c r="V18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W18" s="3">
         <v>-100</v>
@@ -1634,22 +1693,28 @@
         <v>-100</v>
       </c>
       <c r="AA18" s="3">
-        <v>-900</v>
+        <v>-100</v>
       </c>
       <c r="AB18" s="3">
         <v>-100</v>
       </c>
       <c r="AC18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1746,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1732,26 +1799,26 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -1768,10 +1835,16 @@
         <v>0</v>
       </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1779,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
@@ -1788,49 +1861,49 @@
         <v>100</v>
       </c>
       <c r="H21" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
         <v>100</v>
       </c>
       <c r="J21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L21" s="3">
         <v>100</v>
       </c>
       <c r="M21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R21" s="3">
         <v>100</v>
       </c>
       <c r="S21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U21" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="V21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W21" s="3">
         <v>-100</v>
@@ -1845,22 +1918,28 @@
         <v>-100</v>
       </c>
       <c r="AA21" s="3">
-        <v>-800</v>
+        <v>-100</v>
       </c>
       <c r="AB21" s="3">
         <v>-100</v>
       </c>
       <c r="AC21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1873,11 +1952,11 @@
       <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1885,11 +1964,11 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>10</v>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>10</v>
@@ -1924,11 +2003,11 @@
       <c r="W22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -1948,8 +2027,14 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1957,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
@@ -1966,49 +2051,49 @@
         <v>100</v>
       </c>
       <c r="H23" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3">
         <v>100</v>
       </c>
       <c r="J23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L23" s="3">
         <v>100</v>
       </c>
       <c r="M23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P23" s="3">
         <v>0</v>
       </c>
       <c r="Q23" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R23" s="3">
         <v>0</v>
       </c>
       <c r="S23" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T23" s="3">
         <v>0</v>
       </c>
       <c r="U23" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="V23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W23" s="3">
         <v>-100</v>
@@ -2023,22 +2108,28 @@
         <v>-100</v>
       </c>
       <c r="AA23" s="3">
-        <v>-900</v>
+        <v>-100</v>
       </c>
       <c r="AB23" s="3">
         <v>-100</v>
       </c>
       <c r="AC23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2126,8 +2217,14 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,8 +2312,14 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2224,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F26" s="3">
         <v>0</v>
@@ -2233,49 +2336,49 @@
         <v>100</v>
       </c>
       <c r="H26" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3">
         <v>100</v>
       </c>
       <c r="J26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K26" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L26" s="3">
         <v>100</v>
       </c>
       <c r="M26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P26" s="3">
         <v>0</v>
       </c>
       <c r="Q26" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R26" s="3">
         <v>0</v>
       </c>
       <c r="S26" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T26" s="3">
         <v>0</v>
       </c>
       <c r="U26" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="V26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W26" s="3">
         <v>-100</v>
@@ -2290,22 +2393,28 @@
         <v>-100</v>
       </c>
       <c r="AA26" s="3">
-        <v>-900</v>
+        <v>-100</v>
       </c>
       <c r="AB26" s="3">
         <v>-100</v>
       </c>
       <c r="AC26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2313,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="3">
         <v>0</v>
@@ -2322,49 +2431,49 @@
         <v>100</v>
       </c>
       <c r="H27" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3">
         <v>100</v>
       </c>
       <c r="J27" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K27" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P27" s="3">
         <v>0</v>
       </c>
       <c r="Q27" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R27" s="3">
         <v>0</v>
       </c>
       <c r="S27" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T27" s="3">
         <v>0</v>
       </c>
       <c r="U27" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="V27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W27" s="3">
         <v>-100</v>
@@ -2379,22 +2488,28 @@
         <v>-100</v>
       </c>
       <c r="AA27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2597,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2523,56 +2644,62 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-100</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-100</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
         <v>0</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2787,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2882,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2800,25 +2939,25 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z32" s="3">
         <v>0</v>
@@ -2836,10 +2975,16 @@
         <v>0</v>
       </c>
       <c r="AE32" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2847,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F33" s="3">
         <v>0</v>
@@ -2856,49 +3001,49 @@
         <v>100</v>
       </c>
       <c r="H33" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I33" s="3">
         <v>100</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K33" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P33" s="3">
         <v>0</v>
       </c>
       <c r="Q33" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R33" s="3">
         <v>0</v>
       </c>
       <c r="S33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T33" s="3">
         <v>0</v>
       </c>
       <c r="U33" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="V33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W33" s="3">
         <v>-200</v>
@@ -2907,28 +3052,34 @@
         <v>-100</v>
       </c>
       <c r="Y33" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Z33" s="3">
         <v>-100</v>
       </c>
       <c r="AA33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,8 +3167,14 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3025,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F35" s="3">
         <v>0</v>
@@ -3034,49 +3191,49 @@
         <v>100</v>
       </c>
       <c r="H35" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3">
         <v>100</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K35" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O35" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P35" s="3">
         <v>0</v>
       </c>
       <c r="Q35" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R35" s="3">
         <v>0</v>
       </c>
       <c r="S35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T35" s="3">
         <v>0</v>
       </c>
       <c r="U35" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="V35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W35" s="3">
         <v>-200</v>
@@ -3085,122 +3242,134 @@
         <v>-100</v>
       </c>
       <c r="Y35" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Z35" s="3">
         <v>-100</v>
       </c>
       <c r="AA35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3401,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,44 +3436,46 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>500</v>
+      </c>
+      <c r="F41" s="3">
         <v>400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>500</v>
       </c>
-      <c r="H41" s="3">
-        <v>200</v>
-      </c>
-      <c r="I41" s="3">
-        <v>400</v>
-      </c>
       <c r="J41" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="K41" s="3">
         <v>400</v>
       </c>
       <c r="L41" s="3">
+        <v>400</v>
+      </c>
+      <c r="M41" s="3">
+        <v>400</v>
+      </c>
+      <c r="N41" s="3">
         <v>300</v>
       </c>
-      <c r="M41" s="3">
-        <v>100</v>
-      </c>
-      <c r="N41" s="3">
-        <v>100</v>
-      </c>
       <c r="O41" s="3">
         <v>100</v>
       </c>
@@ -3313,10 +3486,10 @@
         <v>100</v>
       </c>
       <c r="R41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T41" s="3">
         <v>0</v>
@@ -3343,19 +3516,25 @@
         <v>0</v>
       </c>
       <c r="AB41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF41" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,13 +3622,19 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E43" s="3">
         <v>500</v>
@@ -3461,22 +3646,22 @@
         <v>500</v>
       </c>
       <c r="H43" s="3">
+        <v>600</v>
+      </c>
+      <c r="I43" s="3">
         <v>500</v>
       </c>
-      <c r="I43" s="3">
-        <v>300</v>
-      </c>
       <c r="J43" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="K43" s="3">
         <v>300</v>
       </c>
       <c r="L43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N43" s="3">
         <v>200</v>
@@ -3488,34 +3673,34 @@
         <v>200</v>
       </c>
       <c r="Q43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R43" s="3">
         <v>200</v>
       </c>
       <c r="S43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T43" s="3">
         <v>200</v>
       </c>
       <c r="U43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W43" s="3">
         <v>100</v>
       </c>
       <c r="X43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y43" s="3">
         <v>100</v>
       </c>
       <c r="Z43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA43" s="3">
         <v>100</v>
@@ -3527,13 +3712,19 @@
         <v>100</v>
       </c>
       <c r="AD43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3580,13 +3771,13 @@
         <v>0</v>
       </c>
       <c r="R44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
       </c>
       <c r="T44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
@@ -3621,8 +3812,14 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3630,19 +3827,19 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H45" s="3">
         <v>0</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3">
         <v>0</v>
@@ -3651,43 +3848,43 @@
         <v>0</v>
       </c>
       <c r="L45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N45" s="3">
         <v>100</v>
       </c>
       <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="P45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3">
-        <v>100</v>
-      </c>
       <c r="S45" s="3">
         <v>0</v>
       </c>
       <c r="T45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
       </c>
       <c r="V45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
       </c>
       <c r="X45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y45" s="3">
         <v>0</v>
@@ -3710,70 +3907,76 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F46" s="3">
         <v>1100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1100</v>
-      </c>
-      <c r="H46" s="3">
-        <v>700</v>
-      </c>
-      <c r="I46" s="3">
-        <v>700</v>
       </c>
       <c r="J46" s="3">
         <v>700</v>
       </c>
       <c r="K46" s="3">
+        <v>700</v>
+      </c>
+      <c r="L46" s="3">
+        <v>700</v>
+      </c>
+      <c r="M46" s="3">
         <v>800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>300</v>
-      </c>
-      <c r="N46" s="3">
-        <v>300</v>
-      </c>
-      <c r="O46" s="3">
-        <v>400</v>
       </c>
       <c r="P46" s="3">
         <v>300</v>
       </c>
       <c r="Q46" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="R46" s="3">
         <v>300</v>
       </c>
       <c r="S46" s="3">
+        <v>200</v>
+      </c>
+      <c r="T46" s="3">
         <v>300</v>
       </c>
-      <c r="T46" s="3">
-        <v>200</v>
-      </c>
       <c r="U46" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V46" s="3">
         <v>200</v>
       </c>
       <c r="W46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X46" s="3">
         <v>200</v>
@@ -3782,13 +3985,13 @@
         <v>100</v>
       </c>
       <c r="Z46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA46" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB46" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC46" s="3">
         <v>200</v>
@@ -3797,15 +4000,21 @@
         <v>200</v>
       </c>
       <c r="AE46" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AF46" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>100</v>
+      <c r="D47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E47" s="3">
         <v>100</v>
@@ -3826,10 +4035,10 @@
         <v>100</v>
       </c>
       <c r="K47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3843,11 +4052,11 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>10</v>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>10</v>
@@ -3861,11 +4070,11 @@
       <c r="V47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
-      </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3888,22 +4097,28 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H48" s="3">
         <v>0</v>
@@ -3932,11 +4147,11 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>10</v>
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>10</v>
@@ -3950,11 +4165,11 @@
       <c r="V48" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
@@ -3977,31 +4192,37 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="F49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -4015,32 +4236,32 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>600</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
-      </c>
-      <c r="T49" s="3">
-        <v>0</v>
-      </c>
       <c r="U49" s="3">
         <v>0</v>
       </c>
       <c r="V49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X49" s="3">
         <v>100</v>
@@ -4049,25 +4270,31 @@
         <v>100</v>
       </c>
       <c r="Z49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB49" s="3">
         <v>200</v>
       </c>
       <c r="AC49" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD49" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE49" s="3">
         <v>300</v>
       </c>
-      <c r="AD49" s="3">
-        <v>200</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4382,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4477,14 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4328,13 +4567,19 @@
         <v>0</v>
       </c>
       <c r="AD52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,28 +4667,34 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1300</v>
       </c>
-      <c r="E54" s="3">
-        <v>1100</v>
-      </c>
       <c r="F54" s="3">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="G54" s="3">
         <v>1100</v>
       </c>
       <c r="H54" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="I54" s="3">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="J54" s="3">
         <v>800</v>
@@ -4452,67 +4703,73 @@
         <v>800</v>
       </c>
       <c r="L54" s="3">
+        <v>800</v>
+      </c>
+      <c r="M54" s="3">
+        <v>800</v>
+      </c>
+      <c r="N54" s="3">
         <v>700</v>
-      </c>
-      <c r="M54" s="3">
-        <v>400</v>
-      </c>
-      <c r="N54" s="3">
-        <v>300</v>
       </c>
       <c r="O54" s="3">
         <v>400</v>
       </c>
       <c r="P54" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>400</v>
+      </c>
+      <c r="R54" s="3">
         <v>800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>300</v>
       </c>
-      <c r="T54" s="3">
-        <v>200</v>
-      </c>
-      <c r="U54" s="3">
-        <v>200</v>
-      </c>
       <c r="V54" s="3">
+        <v>200</v>
+      </c>
+      <c r="W54" s="3">
+        <v>200</v>
+      </c>
+      <c r="X54" s="3">
         <v>300</v>
       </c>
-      <c r="W54" s="3">
-        <v>200</v>
-      </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z54" s="3">
         <v>400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>300</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>400</v>
-      </c>
-      <c r="AB54" s="3">
-        <v>400</v>
       </c>
       <c r="AC54" s="3">
         <v>400</v>
       </c>
       <c r="AD54" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE54" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF54" s="3">
         <v>500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4801,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,13 +4836,15 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E57" s="3">
         <v>100</v>
@@ -4598,10 +4859,10 @@
         <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
@@ -4616,25 +4877,25 @@
         <v>200</v>
       </c>
       <c r="O57" s="3">
+        <v>200</v>
+      </c>
+      <c r="P57" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>200</v>
-      </c>
       <c r="R57" s="3">
+        <v>200</v>
+      </c>
+      <c r="S57" s="3">
+        <v>200</v>
+      </c>
+      <c r="T57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>300</v>
-      </c>
-      <c r="T57" s="3">
-        <v>500</v>
-      </c>
-      <c r="U57" s="3">
-        <v>500</v>
       </c>
       <c r="V57" s="3">
         <v>500</v>
@@ -4655,10 +4916,10 @@
         <v>500</v>
       </c>
       <c r="AB57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AC57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AD57" s="3">
         <v>400</v>
@@ -4666,8 +4927,14 @@
       <c r="AE57" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4705,10 +4972,10 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>100</v>
@@ -4738,60 +5005,66 @@
         <v>100</v>
       </c>
       <c r="Z58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD58" s="3">
         <v>100</v>
       </c>
       <c r="AE58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1000</v>
-      </c>
-      <c r="M59" s="3">
-        <v>700</v>
-      </c>
-      <c r="N59" s="3">
-        <v>700</v>
       </c>
       <c r="O59" s="3">
         <v>700</v>
@@ -4800,34 +5073,34 @@
         <v>700</v>
       </c>
       <c r="Q59" s="3">
+        <v>700</v>
+      </c>
+      <c r="R59" s="3">
+        <v>700</v>
+      </c>
+      <c r="S59" s="3">
         <v>800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1000</v>
-      </c>
-      <c r="T59" s="3">
-        <v>800</v>
-      </c>
-      <c r="U59" s="3">
-        <v>800</v>
       </c>
       <c r="V59" s="3">
         <v>800</v>
       </c>
       <c r="W59" s="3">
+        <v>800</v>
+      </c>
+      <c r="X59" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y59" s="3">
         <v>600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>600</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>400</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>400</v>
       </c>
       <c r="AA59" s="3">
         <v>400</v>
@@ -4836,54 +5109,60 @@
         <v>400</v>
       </c>
       <c r="AC59" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AD59" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AE59" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AF59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F60" s="3">
         <v>1100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>900</v>
-      </c>
-      <c r="N60" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O60" s="3">
-        <v>1100</v>
       </c>
       <c r="P60" s="3">
         <v>1000</v>
@@ -4892,49 +5171,55 @@
         <v>1100</v>
       </c>
       <c r="R60" s="3">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="S60" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="T60" s="3">
         <v>1400</v>
       </c>
       <c r="U60" s="3">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="V60" s="3">
         <v>1400</v>
       </c>
       <c r="W60" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y60" s="3">
         <v>1300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>800</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>900</v>
       </c>
       <c r="AC60" s="3">
         <v>800</v>
       </c>
       <c r="AD60" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE60" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF60" s="3">
         <v>700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4963,10 +5248,10 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>100</v>
@@ -4978,10 +5263,10 @@
         <v>100</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -5008,22 +5293,28 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
       <c r="AC61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
       <c r="AE61" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5049,13 +5340,13 @@
         <v>100</v>
       </c>
       <c r="K62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M62" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -5070,10 +5361,10 @@
         <v>0</v>
       </c>
       <c r="R62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T62" s="3">
         <v>100</v>
@@ -5082,13 +5373,13 @@
         <v>100</v>
       </c>
       <c r="V62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W62" s="3">
         <v>100</v>
       </c>
       <c r="X62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y62" s="3">
         <v>100</v>
@@ -5106,13 +5397,19 @@
         <v>100</v>
       </c>
       <c r="AD62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5497,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5592,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5687,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F66" s="3">
         <v>1200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1000</v>
-      </c>
-      <c r="N66" s="3">
-        <v>1100</v>
-      </c>
-      <c r="O66" s="3">
-        <v>1200</v>
       </c>
       <c r="P66" s="3">
         <v>1100</v>
       </c>
       <c r="Q66" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R66" s="3">
         <v>1100</v>
       </c>
-      <c r="R66" s="3">
-        <v>1500</v>
-      </c>
       <c r="S66" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="T66" s="3">
         <v>1500</v>
       </c>
       <c r="U66" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="V66" s="3">
         <v>1500</v>
       </c>
       <c r="W66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="X66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y66" s="3">
         <v>1400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5821,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5912,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6007,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +6102,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,8 +6197,14 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -5868,85 +6215,91 @@
         <v>-15200</v>
       </c>
       <c r="F72" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="H72" s="3">
         <v>-15300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-15300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-15400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-15500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-15600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-15700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-15900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-15900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-16000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-16100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-16200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-16300</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-16300</v>
-      </c>
-      <c r="S72" s="3">
-        <v>-16200</v>
       </c>
       <c r="T72" s="3">
         <v>-16300</v>
       </c>
       <c r="U72" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="V72" s="3">
         <v>-16300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="X72" s="3">
         <v>-16200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-16000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-15600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-15500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-15400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-15300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-14700</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6387,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6482,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,8 +6577,14 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6227,82 +6598,88 @@
         <v>0</v>
       </c>
       <c r="G76" s="3">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3">
         <v>-100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-1200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-1300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-1300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-1200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-1200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>-800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-500</v>
-      </c>
-      <c r="AC76" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>-200</v>
       </c>
       <c r="AE76" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG76" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,102 +6767,114 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6493,7 +6882,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F81" s="3">
         <v>0</v>
@@ -6502,49 +6891,49 @@
         <v>100</v>
       </c>
       <c r="H81" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I81" s="3">
         <v>100</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K81" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O81" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P81" s="3">
         <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R81" s="3">
         <v>0</v>
       </c>
       <c r="S81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T81" s="3">
         <v>0</v>
       </c>
       <c r="U81" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="V81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W81" s="3">
         <v>-200</v>
@@ -6553,28 +6942,34 @@
         <v>-100</v>
       </c>
       <c r="Y81" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Z81" s="3">
         <v>-100</v>
       </c>
       <c r="AA81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +7001,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6645,16 +7042,16 @@
         <v>0</v>
       </c>
       <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
         <v>-100</v>
       </c>
-      <c r="P83" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -6681,22 +7078,28 @@
         <v>0</v>
       </c>
       <c r="AA83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
       </c>
       <c r="AC83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7187,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7282,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7377,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7472,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,64 +7567,70 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E89" s="3">
         <v>100</v>
       </c>
       <c r="F89" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="G89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H89" s="3">
         <v>-200</v>
       </c>
       <c r="I89" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L89" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M89" s="3">
         <v>100</v>
       </c>
       <c r="N89" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R89" s="3">
         <v>-100</v>
       </c>
       <c r="S89" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
@@ -7206,16 +7639,16 @@
         <v>-100</v>
       </c>
       <c r="X89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA89" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AB89" s="3">
         <v>0</v>
@@ -7227,10 +7660,16 @@
         <v>0</v>
       </c>
       <c r="AE89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+        <v>-200</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,13 +7701,15 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -7291,17 +7732,17 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>10</v>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>10</v>
@@ -7309,8 +7750,8 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -7351,8 +7792,14 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7887,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,13 +7982,19 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -7558,20 +8017,20 @@
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>10</v>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -7591,35 +8050,41 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="3" t="s">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB94" s="3" t="s">
+      <c r="AD94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +8116,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +8207,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8302,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8397,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8492,14 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8049,55 +8540,61 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>100</v>
+      </c>
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
-        <v>100</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>300</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>200</v>
-      </c>
       <c r="AD100" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,43 +8682,49 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E102" s="3">
         <v>100</v>
       </c>
       <c r="F102" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H102" s="3">
         <v>-200</v>
       </c>
       <c r="I102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J102" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L102" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
@@ -8230,13 +8733,13 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
       </c>
       <c r="S102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T102" s="3">
         <v>0</v>
@@ -8266,12 +8769,18 @@
         <v>0</v>
       </c>
       <c r="AC102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD102" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CLRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CLRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>CLRI</t>
   </si>
@@ -656,143 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -806,7 +810,7 @@
         <v>600</v>
       </c>
       <c r="G8" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H8" s="3">
         <v>500</v>
@@ -824,7 +828,7 @@
         <v>500</v>
       </c>
       <c r="M8" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N8" s="3">
         <v>400</v>
@@ -842,28 +846,28 @@
         <v>400</v>
       </c>
       <c r="S8" s="3">
+        <v>400</v>
+      </c>
+      <c r="T8" s="3">
         <v>500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>300</v>
       </c>
-      <c r="X8" s="3">
-        <v>200</v>
-      </c>
       <c r="Y8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA8" s="3">
         <v>200</v>
@@ -872,22 +876,25 @@
         <v>200</v>
       </c>
       <c r="AC8" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD8" s="3">
         <v>300</v>
       </c>
-      <c r="AD8" s="3">
-        <v>200</v>
-      </c>
       <c r="AE8" s="3">
         <v>200</v>
       </c>
       <c r="AF8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AG8" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -949,17 +956,17 @@
         <v>100</v>
       </c>
       <c r="W9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X9" s="3">
         <v>0</v>
       </c>
       <c r="Y9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3">
         <v>-100</v>
       </c>
-      <c r="Z9" s="3">
-        <v>0</v>
-      </c>
       <c r="AA9" s="3">
         <v>0</v>
       </c>
@@ -967,22 +974,25 @@
         <v>0</v>
       </c>
       <c r="AC9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -996,7 +1006,7 @@
         <v>500</v>
       </c>
       <c r="G10" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H10" s="3">
         <v>400</v>
@@ -1014,7 +1024,7 @@
         <v>400</v>
       </c>
       <c r="M10" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N10" s="3">
         <v>300</v>
@@ -1032,22 +1042,22 @@
         <v>300</v>
       </c>
       <c r="S10" s="3">
+        <v>300</v>
+      </c>
+      <c r="T10" s="3">
         <v>400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>300</v>
       </c>
-      <c r="U10" s="3">
-        <v>200</v>
-      </c>
       <c r="V10" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W10" s="3">
         <v>300</v>
       </c>
       <c r="X10" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y10" s="3">
         <v>200</v>
@@ -1068,7 +1078,7 @@
         <v>200</v>
       </c>
       <c r="AE10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF10" s="3">
         <v>100</v>
@@ -1076,8 +1086,11 @@
       <c r="AG10" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1132,10 +1146,10 @@
         <v>0</v>
       </c>
       <c r="I12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -1165,16 +1179,16 @@
         <v>0</v>
       </c>
       <c r="T12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V12" s="3">
         <v>0</v>
       </c>
       <c r="W12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X12" s="3">
         <v>100</v>
@@ -1183,10 +1197,10 @@
         <v>100</v>
       </c>
       <c r="Z12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="3">
         <v>100</v>
@@ -1195,7 +1209,7 @@
         <v>100</v>
       </c>
       <c r="AD12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE12" s="3">
         <v>0</v>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1301,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1315,32 +1335,32 @@
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>10</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>10</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>10</v>
@@ -1357,23 +1377,23 @@
       <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>10</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
@@ -1381,14 +1401,14 @@
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
-        <v>200</v>
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AE14" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AF14" s="3">
         <v>200</v>
@@ -1396,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,14 +1463,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="s">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="3">
-        <v>100</v>
-      </c>
       <c r="S15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1477,22 +1500,25 @@
         <v>0</v>
       </c>
       <c r="AC15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,8 +1549,9 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1538,13 +1565,13 @@
         <v>600</v>
       </c>
       <c r="G17" s="3">
+        <v>600</v>
+      </c>
+      <c r="H17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>400</v>
       </c>
       <c r="J17" s="3">
         <v>400</v>
@@ -1553,31 +1580,31 @@
         <v>400</v>
       </c>
       <c r="L17" s="3">
+        <v>400</v>
+      </c>
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="M17" s="3">
-        <v>200</v>
-      </c>
       <c r="N17" s="3">
+        <v>200</v>
+      </c>
+      <c r="O17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3">
-        <v>200</v>
-      </c>
       <c r="R17" s="3">
+        <v>200</v>
+      </c>
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>500</v>
-      </c>
-      <c r="T17" s="3">
-        <v>400</v>
       </c>
       <c r="U17" s="3">
         <v>400</v>
@@ -1589,13 +1616,13 @@
         <v>400</v>
       </c>
       <c r="X17" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y17" s="3">
         <v>300</v>
       </c>
-      <c r="Y17" s="3">
-        <v>200</v>
-      </c>
       <c r="Z17" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AA17" s="3">
         <v>300</v>
@@ -1604,22 +1631,25 @@
         <v>300</v>
       </c>
       <c r="AC17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD17" s="3">
         <v>1200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1633,13 +1663,13 @@
         <v>0</v>
       </c>
       <c r="G18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3">
         <v>100</v>
@@ -1648,25 +1678,25 @@
         <v>100</v>
       </c>
       <c r="L18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R18" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S18" s="3">
         <v>0</v>
@@ -1675,13 +1705,13 @@
         <v>0</v>
       </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
       <c r="W18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X18" s="3">
         <v>-100</v>
@@ -1699,22 +1729,25 @@
         <v>-100</v>
       </c>
       <c r="AC18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,8 +1781,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1805,11 +1839,11 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1817,11 +1851,11 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -1841,10 +1875,13 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1858,40 +1895,40 @@
         <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L21" s="3">
         <v>100</v>
       </c>
       <c r="M21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O21" s="3">
         <v>100</v>
       </c>
       <c r="P21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21" s="3">
         <v>0</v>
       </c>
       <c r="R21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S21" s="3">
         <v>100</v>
@@ -1900,13 +1937,13 @@
         <v>100</v>
       </c>
       <c r="U21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V21" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X21" s="3">
         <v>-100</v>
@@ -1924,22 +1961,25 @@
         <v>-100</v>
       </c>
       <c r="AC21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-600</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>-400</v>
       </c>
       <c r="AG21" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1958,8 +1998,8 @@
       <c r="H22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1970,8 +2010,8 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>10</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>10</v>
@@ -2009,8 +2049,8 @@
       <c r="Y22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -2033,8 +2073,11 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2048,40 +2091,40 @@
         <v>0</v>
       </c>
       <c r="G23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L23" s="3">
         <v>100</v>
       </c>
       <c r="M23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O23" s="3">
         <v>100</v>
       </c>
       <c r="P23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R23" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S23" s="3">
         <v>0</v>
@@ -2090,13 +2133,13 @@
         <v>0</v>
       </c>
       <c r="U23" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X23" s="3">
         <v>-100</v>
@@ -2114,22 +2157,25 @@
         <v>-100</v>
       </c>
       <c r="AC23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-600</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>-400</v>
       </c>
       <c r="AG23" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2223,8 +2269,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,8 +2367,11 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2333,40 +2385,40 @@
         <v>0</v>
       </c>
       <c r="G26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L26" s="3">
         <v>100</v>
       </c>
       <c r="M26" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O26" s="3">
         <v>100</v>
       </c>
       <c r="P26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R26" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S26" s="3">
         <v>0</v>
@@ -2375,13 +2427,13 @@
         <v>0</v>
       </c>
       <c r="U26" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X26" s="3">
         <v>-100</v>
@@ -2399,22 +2451,25 @@
         <v>-100</v>
       </c>
       <c r="AC26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-600</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>-400</v>
       </c>
       <c r="AG26" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2422,46 +2477,46 @@
         <v>0</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-100</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O27" s="3">
         <v>100</v>
       </c>
       <c r="P27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R27" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S27" s="3">
         <v>0</v>
@@ -2470,13 +2525,13 @@
         <v>0</v>
       </c>
       <c r="U27" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X27" s="3">
         <v>-100</v>
@@ -2494,22 +2549,25 @@
         <v>-100</v>
       </c>
       <c r="AC27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-600</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>-400</v>
       </c>
       <c r="AG27" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2650,21 +2711,21 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
       <c r="T29" s="3">
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-100</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
         <v>0</v>
       </c>
@@ -2672,11 +2733,11 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-100</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
@@ -2686,20 +2747,23 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3">
         <v>0</v>
       </c>
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,8 +2955,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2945,11 +3015,11 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -2957,10 +3027,10 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA32" s="3">
         <v>0</v>
@@ -2981,10 +3051,13 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2992,46 +3065,46 @@
         <v>0</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-100</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O33" s="3">
         <v>100</v>
       </c>
       <c r="P33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R33" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S33" s="3">
         <v>0</v>
@@ -3040,22 +3113,22 @@
         <v>0</v>
       </c>
       <c r="U33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-100</v>
       </c>
       <c r="AA33" s="3">
         <v>-100</v>
@@ -3064,22 +3137,25 @@
         <v>-100</v>
       </c>
       <c r="AC33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-600</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>-400</v>
       </c>
       <c r="AG33" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,8 +3249,11 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3182,46 +3261,46 @@
         <v>0</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-100</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O35" s="3">
         <v>100</v>
       </c>
       <c r="P35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q35" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R35" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S35" s="3">
         <v>0</v>
@@ -3230,22 +3309,22 @@
         <v>0</v>
       </c>
       <c r="U35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-100</v>
       </c>
       <c r="AA35" s="3">
         <v>-100</v>
@@ -3254,122 +3333,128 @@
         <v>-100</v>
       </c>
       <c r="AC35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-600</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>-400</v>
       </c>
       <c r="AG35" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,34 +3524,35 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>700</v>
+      </c>
+      <c r="E41" s="3">
         <v>800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>500</v>
-      </c>
-      <c r="F41" s="3">
-        <v>400</v>
       </c>
       <c r="G41" s="3">
         <v>400</v>
       </c>
       <c r="H41" s="3">
+        <v>400</v>
+      </c>
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>500</v>
       </c>
-      <c r="J41" s="3">
-        <v>200</v>
-      </c>
       <c r="K41" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="L41" s="3">
         <v>400</v>
@@ -3474,11 +3561,11 @@
         <v>400</v>
       </c>
       <c r="N41" s="3">
+        <v>400</v>
+      </c>
+      <c r="O41" s="3">
         <v>300</v>
       </c>
-      <c r="O41" s="3">
-        <v>100</v>
-      </c>
       <c r="P41" s="3">
         <v>100</v>
       </c>
@@ -3492,7 +3579,7 @@
         <v>100</v>
       </c>
       <c r="T41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U41" s="3">
         <v>0</v>
@@ -3522,19 +3609,22 @@
         <v>0</v>
       </c>
       <c r="AD41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE41" s="3">
         <v>100</v>
       </c>
       <c r="AF41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AG41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,34 +3718,37 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E43" s="3">
         <v>500</v>
       </c>
       <c r="F43" s="3">
+        <v>500</v>
+      </c>
+      <c r="G43" s="3">
         <v>600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>600</v>
-      </c>
-      <c r="I43" s="3">
-        <v>500</v>
       </c>
       <c r="J43" s="3">
         <v>500</v>
       </c>
       <c r="K43" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="L43" s="3">
         <v>300</v>
@@ -3664,7 +3757,7 @@
         <v>300</v>
       </c>
       <c r="N43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O43" s="3">
         <v>200</v>
@@ -3679,10 +3772,10 @@
         <v>200</v>
       </c>
       <c r="S43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U43" s="3">
         <v>200</v>
@@ -3691,7 +3784,7 @@
         <v>200</v>
       </c>
       <c r="W43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X43" s="3">
         <v>100</v>
@@ -3700,10 +3793,10 @@
         <v>100</v>
       </c>
       <c r="Z43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB43" s="3">
         <v>100</v>
@@ -3718,13 +3811,16 @@
         <v>100</v>
       </c>
       <c r="AF43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3777,10 +3873,10 @@
         <v>0</v>
       </c>
       <c r="T44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -3818,8 +3914,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3833,16 +3932,16 @@
         <v>100</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H45" s="3">
         <v>0</v>
       </c>
       <c r="I45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -3854,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="N45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O45" s="3">
         <v>100</v>
@@ -3863,19 +3962,19 @@
         <v>100</v>
       </c>
       <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
       <c r="T45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
@@ -3884,10 +3983,10 @@
         <v>0</v>
       </c>
       <c r="X45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z45" s="3">
         <v>0</v>
@@ -3913,31 +4012,34 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1100</v>
-      </c>
-      <c r="J46" s="3">
-        <v>700</v>
       </c>
       <c r="K46" s="3">
         <v>700</v>
@@ -3946,34 +4048,34 @@
         <v>700</v>
       </c>
       <c r="M46" s="3">
+        <v>700</v>
+      </c>
+      <c r="N46" s="3">
         <v>800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>600</v>
-      </c>
-      <c r="O46" s="3">
-        <v>300</v>
       </c>
       <c r="P46" s="3">
         <v>300</v>
       </c>
       <c r="Q46" s="3">
+        <v>300</v>
+      </c>
+      <c r="R46" s="3">
         <v>400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>300</v>
       </c>
-      <c r="S46" s="3">
-        <v>200</v>
-      </c>
       <c r="T46" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U46" s="3">
         <v>300</v>
       </c>
       <c r="V46" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W46" s="3">
         <v>200</v>
@@ -3982,19 +4084,19 @@
         <v>200</v>
       </c>
       <c r="Y46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z46" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB46" s="3">
         <v>100</v>
       </c>
       <c r="AC46" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD46" s="3">
         <v>200</v>
@@ -4006,19 +4108,22 @@
         <v>200</v>
       </c>
       <c r="AG46" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="3">
+        <v>100</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="3">
-        <v>100</v>
-      </c>
       <c r="F47" s="3">
         <v>100</v>
       </c>
@@ -4041,7 +4146,7 @@
         <v>100</v>
       </c>
       <c r="M47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4058,8 +4163,8 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>10</v>
+      <c r="S47" s="3">
+        <v>0</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>10</v>
@@ -4076,8 +4181,8 @@
       <c r="X47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -4103,8 +4208,11 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4115,13 +4223,13 @@
         <v>0</v>
       </c>
       <c r="F48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3">
         <v>100</v>
       </c>
       <c r="H48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I48" s="3">
         <v>0</v>
@@ -4153,8 +4261,8 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>10</v>
+      <c r="S48" s="3">
+        <v>0</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>10</v>
@@ -4171,8 +4279,8 @@
       <c r="X48" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
+      <c r="Y48" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
@@ -4198,19 +4306,22 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -4224,8 +4335,8 @@
       <c r="J49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -4242,21 +4353,21 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3" t="s">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="R49" s="3">
-        <v>500</v>
       </c>
       <c r="S49" s="3">
         <v>500</v>
       </c>
       <c r="T49" s="3">
+        <v>500</v>
+      </c>
+      <c r="U49" s="3">
         <v>600</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
-      </c>
       <c r="V49" s="3">
         <v>0</v>
       </c>
@@ -4264,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="X49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y49" s="3">
         <v>100</v>
@@ -4276,7 +4387,7 @@
         <v>100</v>
       </c>
       <c r="AB49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC49" s="3">
         <v>200</v>
@@ -4285,16 +4396,19 @@
         <v>200</v>
       </c>
       <c r="AE49" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF49" s="3">
         <v>300</v>
       </c>
-      <c r="AF49" s="3">
-        <v>200</v>
-      </c>
       <c r="AG49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,8 +4600,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4573,13 +4693,16 @@
         <v>0</v>
       </c>
       <c r="AF52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,31 +4796,34 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1600</v>
-      </c>
-      <c r="E54" s="3">
-        <v>1300</v>
       </c>
       <c r="F54" s="3">
         <v>1300</v>
       </c>
       <c r="G54" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H54" s="3">
         <v>1100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1100</v>
-      </c>
-      <c r="J54" s="3">
-        <v>800</v>
       </c>
       <c r="K54" s="3">
         <v>800</v>
@@ -4709,52 +4835,52 @@
         <v>800</v>
       </c>
       <c r="N54" s="3">
+        <v>800</v>
+      </c>
+      <c r="O54" s="3">
         <v>700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>400</v>
-      </c>
-      <c r="R54" s="3">
-        <v>800</v>
       </c>
       <c r="S54" s="3">
         <v>800</v>
       </c>
       <c r="T54" s="3">
+        <v>800</v>
+      </c>
+      <c r="U54" s="3">
         <v>900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>300</v>
       </c>
-      <c r="V54" s="3">
-        <v>200</v>
-      </c>
       <c r="W54" s="3">
         <v>200</v>
       </c>
       <c r="X54" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y54" s="3">
         <v>300</v>
       </c>
-      <c r="Y54" s="3">
-        <v>200</v>
-      </c>
       <c r="Z54" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA54" s="3">
         <v>400</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>300</v>
       </c>
       <c r="AB54" s="3">
         <v>300</v>
       </c>
       <c r="AC54" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AD54" s="3">
         <v>400</v>
@@ -4763,13 +4889,16 @@
         <v>400</v>
       </c>
       <c r="AF54" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG54" s="3">
         <v>500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,8 +4968,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4847,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="E57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
@@ -4865,7 +4996,7 @@
         <v>100</v>
       </c>
       <c r="K57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
@@ -4883,22 +5014,22 @@
         <v>200</v>
       </c>
       <c r="Q57" s="3">
+        <v>200</v>
+      </c>
+      <c r="R57" s="3">
         <v>300</v>
       </c>
-      <c r="R57" s="3">
-        <v>200</v>
-      </c>
       <c r="S57" s="3">
         <v>200</v>
       </c>
       <c r="T57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U57" s="3">
         <v>300</v>
       </c>
       <c r="V57" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="W57" s="3">
         <v>500</v>
@@ -4922,7 +5053,7 @@
         <v>500</v>
       </c>
       <c r="AD57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AE57" s="3">
         <v>400</v>
@@ -4933,8 +5064,11 @@
       <c r="AG57" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4978,7 +5112,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>100</v>
@@ -5011,13 +5145,13 @@
         <v>100</v>
       </c>
       <c r="AB58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AD58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="3">
         <v>100</v>
@@ -5026,10 +5160,13 @@
         <v>100</v>
       </c>
       <c r="AG58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5037,37 +5174,37 @@
         <v>1500</v>
       </c>
       <c r="E59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F59" s="3">
         <v>1100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>700</v>
-      </c>
-      <c r="K59" s="3">
-        <v>800</v>
       </c>
       <c r="L59" s="3">
         <v>800</v>
       </c>
       <c r="M59" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="N59" s="3">
         <v>1000</v>
       </c>
       <c r="O59" s="3">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="P59" s="3">
         <v>700</v>
@@ -5079,16 +5216,16 @@
         <v>700</v>
       </c>
       <c r="S59" s="3">
+        <v>700</v>
+      </c>
+      <c r="T59" s="3">
         <v>800</v>
-      </c>
-      <c r="T59" s="3">
-        <v>1000</v>
       </c>
       <c r="U59" s="3">
         <v>1000</v>
       </c>
       <c r="V59" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="W59" s="3">
         <v>800</v>
@@ -5097,13 +5234,13 @@
         <v>800</v>
       </c>
       <c r="Y59" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="Z59" s="3">
         <v>600</v>
       </c>
       <c r="AA59" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AB59" s="3">
         <v>400</v>
@@ -5115,111 +5252,117 @@
         <v>400</v>
       </c>
       <c r="AE59" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AF59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AG59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1100</v>
-      </c>
-      <c r="G60" s="3">
-        <v>900</v>
       </c>
       <c r="H60" s="3">
         <v>900</v>
       </c>
       <c r="I60" s="3">
+        <v>900</v>
+      </c>
+      <c r="J60" s="3">
         <v>1100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1200</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>1000</v>
       </c>
       <c r="AB60" s="3">
         <v>1000</v>
       </c>
       <c r="AC60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD60" s="3">
         <v>800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5254,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>100</v>
@@ -5269,7 +5412,7 @@
         <v>100</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -5299,10 +5442,10 @@
         <v>0</v>
       </c>
       <c r="AC61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
@@ -5311,10 +5454,13 @@
         <v>0</v>
       </c>
       <c r="AG61" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5346,10 +5492,10 @@
         <v>100</v>
       </c>
       <c r="M62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N62" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -5367,7 +5513,7 @@
         <v>0</v>
       </c>
       <c r="T62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U62" s="3">
         <v>100</v>
@@ -5379,10 +5525,10 @@
         <v>100</v>
       </c>
       <c r="X62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z62" s="3">
         <v>100</v>
@@ -5403,13 +5549,16 @@
         <v>100</v>
       </c>
       <c r="AF62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,8 +5848,11 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5702,52 +5860,52 @@
         <v>1600</v>
       </c>
       <c r="E66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F66" s="3">
         <v>1300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1200</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1000</v>
       </c>
       <c r="H66" s="3">
         <v>1000</v>
       </c>
       <c r="I66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J66" s="3">
         <v>1200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>900</v>
-      </c>
-      <c r="K66" s="3">
-        <v>1100</v>
       </c>
       <c r="L66" s="3">
         <v>1100</v>
       </c>
       <c r="M66" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="N66" s="3">
         <v>1300</v>
       </c>
       <c r="O66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P66" s="3">
         <v>1000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1200</v>
-      </c>
-      <c r="R66" s="3">
-        <v>1100</v>
       </c>
       <c r="S66" s="3">
         <v>1100</v>
       </c>
       <c r="T66" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="U66" s="3">
         <v>1500</v>
@@ -5756,40 +5914,43 @@
         <v>1500</v>
       </c>
       <c r="W66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X66" s="3">
         <v>1600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1500</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>1400</v>
       </c>
       <c r="Z66" s="3">
         <v>1400</v>
       </c>
       <c r="AA66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AB66" s="3">
         <v>1200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>1000</v>
       </c>
       <c r="AD66" s="3">
         <v>1000</v>
       </c>
       <c r="AE66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF66" s="3">
         <v>800</v>
-      </c>
-      <c r="AF66" s="3">
-        <v>700</v>
       </c>
       <c r="AG66" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,8 +6374,11 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6221,85 +6395,88 @@
         <v>-15200</v>
       </c>
       <c r="H72" s="3">
-        <v>-15300</v>
+        <v>-15200</v>
       </c>
       <c r="I72" s="3">
         <v>-15300</v>
       </c>
       <c r="J72" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="K72" s="3">
         <v>-15400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-15500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-15600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-15700</v>
-      </c>
-      <c r="N72" s="3">
-        <v>-15900</v>
       </c>
       <c r="O72" s="3">
         <v>-15900</v>
       </c>
       <c r="P72" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-16100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-16200</v>
-      </c>
-      <c r="S72" s="3">
-        <v>-16300</v>
       </c>
       <c r="T72" s="3">
         <v>-16300</v>
       </c>
       <c r="U72" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="V72" s="3">
         <v>-16200</v>
-      </c>
-      <c r="V72" s="3">
-        <v>-16300</v>
       </c>
       <c r="W72" s="3">
         <v>-16300</v>
       </c>
       <c r="X72" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-16200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-15900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-15700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-15600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-15500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-15400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-15300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-15000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-14700</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,8 +6766,11 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6604,82 +6790,85 @@
         <v>0</v>
       </c>
       <c r="I76" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J76" s="3">
         <v>-100</v>
       </c>
       <c r="K76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L76" s="3">
         <v>-300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-700</v>
-      </c>
-      <c r="P76" s="3">
-        <v>-800</v>
       </c>
       <c r="Q76" s="3">
         <v>-800</v>
       </c>
       <c r="R76" s="3">
-        <v>-400</v>
+        <v>-800</v>
       </c>
       <c r="S76" s="3">
         <v>-400</v>
       </c>
       <c r="T76" s="3">
+        <v>-400</v>
+      </c>
+      <c r="U76" s="3">
         <v>-600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-1200</v>
-      </c>
-      <c r="V76" s="3">
-        <v>-1300</v>
       </c>
       <c r="W76" s="3">
         <v>-1300</v>
       </c>
       <c r="X76" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="Y76" s="3">
         <v>-1200</v>
       </c>
       <c r="Z76" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AA76" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,108 +6962,114 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6882,46 +7077,46 @@
         <v>0</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-100</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J81" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M81" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O81" s="3">
         <v>100</v>
       </c>
       <c r="P81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q81" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R81" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S81" s="3">
         <v>0</v>
@@ -6930,22 +7125,22 @@
         <v>0</v>
       </c>
       <c r="U81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-100</v>
       </c>
       <c r="AA81" s="3">
         <v>-100</v>
@@ -6954,22 +7149,25 @@
         <v>-100</v>
       </c>
       <c r="AC81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-600</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>-400</v>
       </c>
       <c r="AG81" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7048,13 +7247,13 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
         <v>-100</v>
       </c>
-      <c r="R83" s="3">
-        <v>100</v>
-      </c>
       <c r="S83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -7084,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="AC83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE83" s="3">
         <v>0</v>
@@ -7095,11 +7294,14 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-      <c r="AG83" s="3" t="s">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
         <v>400</v>
       </c>
-      <c r="E89" s="3">
-        <v>100</v>
-      </c>
       <c r="F89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H89" s="3">
+        <v>100</v>
+      </c>
+      <c r="I89" s="3">
         <v>-200</v>
       </c>
-      <c r="I89" s="3">
-        <v>200</v>
-      </c>
       <c r="J89" s="3">
+        <v>200</v>
+      </c>
+      <c r="K89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
         <v>0</v>
       </c>
       <c r="M89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N89" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O89" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
       </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
-        <v>200</v>
-      </c>
       <c r="T89" s="3">
+        <v>200</v>
+      </c>
+      <c r="U89" s="3">
         <v>-100</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
         <v>0</v>
       </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Z89" s="3">
-        <v>100</v>
-      </c>
       <c r="AA89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB89" s="3">
         <v>0</v>
       </c>
       <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-200</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
-      </c>
       <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-200</v>
       </c>
-      <c r="AF89" s="3">
-        <v>0</v>
-      </c>
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7712,7 +7933,7 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -7738,8 +7959,8 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>10</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>10</v>
@@ -7747,14 +7968,14 @@
       <c r="P91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
+      <c r="Q91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -7798,8 +8019,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,8 +8215,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7997,7 +8227,7 @@
         <v>-100</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -8023,8 +8253,8 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>10</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>10</v>
@@ -8032,8 +8262,8 @@
       <c r="P94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -8056,26 +8286,26 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-      <c r="Y94" s="3" t="s">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>10</v>
+      <c r="AC94" s="3">
+        <v>0</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
+      <c r="AE94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF94" s="3">
         <v>0</v>
@@ -8083,8 +8313,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,8 +8741,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8546,16 +8792,16 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>100</v>
+      </c>
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
-        <v>100</v>
-      </c>
       <c r="U100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -8564,37 +8810,40 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
-        <v>100</v>
-      </c>
       <c r="AA100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>300</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AF100" s="3">
         <v>200</v>
       </c>
       <c r="AG100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,46 +8937,49 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
-        <v>100</v>
-      </c>
       <c r="F102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>100</v>
+      </c>
+      <c r="I102" s="3">
         <v>-200</v>
       </c>
-      <c r="I102" s="3">
-        <v>200</v>
-      </c>
       <c r="J102" s="3">
+        <v>200</v>
+      </c>
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
       <c r="M102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N102" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P102" s="3">
         <v>0</v>
@@ -8739,10 +8991,10 @@
         <v>0</v>
       </c>
       <c r="S102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U102" s="3">
         <v>0</v>
@@ -8775,12 +9027,15 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF102" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AG102" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CLRI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CLRI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>CLRI</t>
   </si>
@@ -656,155 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E8" s="3">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="F8" s="3">
         <v>600</v>
@@ -813,7 +817,7 @@
         <v>600</v>
       </c>
       <c r="H8" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I8" s="3">
         <v>500</v>
@@ -831,7 +835,7 @@
         <v>500</v>
       </c>
       <c r="N8" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O8" s="3">
         <v>400</v>
@@ -849,28 +853,28 @@
         <v>400</v>
       </c>
       <c r="T8" s="3">
+        <v>400</v>
+      </c>
+      <c r="U8" s="3">
         <v>500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>300</v>
       </c>
-      <c r="Y8" s="3">
-        <v>200</v>
-      </c>
       <c r="Z8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB8" s="3">
         <v>200</v>
@@ -879,30 +883,33 @@
         <v>200</v>
       </c>
       <c r="AD8" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE8" s="3">
         <v>300</v>
       </c>
-      <c r="AE8" s="3">
-        <v>200</v>
-      </c>
       <c r="AF8" s="3">
         <v>200</v>
       </c>
       <c r="AG8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH8" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E9" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F9" s="3">
         <v>100</v>
@@ -959,17 +966,17 @@
         <v>100</v>
       </c>
       <c r="X9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y9" s="3">
         <v>0</v>
       </c>
       <c r="Z9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="3">
         <v>-100</v>
       </c>
-      <c r="AA9" s="3">
-        <v>0</v>
-      </c>
       <c r="AB9" s="3">
         <v>0</v>
       </c>
@@ -977,30 +984,33 @@
         <v>0</v>
       </c>
       <c r="AD9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E10" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="F10" s="3">
         <v>500</v>
@@ -1009,7 +1019,7 @@
         <v>500</v>
       </c>
       <c r="H10" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I10" s="3">
         <v>400</v>
@@ -1027,7 +1037,7 @@
         <v>400</v>
       </c>
       <c r="N10" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O10" s="3">
         <v>300</v>
@@ -1045,22 +1055,22 @@
         <v>300</v>
       </c>
       <c r="T10" s="3">
+        <v>300</v>
+      </c>
+      <c r="U10" s="3">
         <v>400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>300</v>
       </c>
-      <c r="V10" s="3">
-        <v>200</v>
-      </c>
       <c r="W10" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X10" s="3">
         <v>300</v>
       </c>
       <c r="Y10" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Z10" s="3">
         <v>200</v>
@@ -1081,7 +1091,7 @@
         <v>200</v>
       </c>
       <c r="AF10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AG10" s="3">
         <v>100</v>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1149,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12" s="3">
         <v>0</v>
@@ -1182,16 +1196,16 @@
         <v>0</v>
       </c>
       <c r="U12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W12" s="3">
         <v>0</v>
       </c>
       <c r="X12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="3">
         <v>100</v>
@@ -1200,10 +1214,10 @@
         <v>100</v>
       </c>
       <c r="AA12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="3">
         <v>100</v>
@@ -1212,7 +1226,7 @@
         <v>100</v>
       </c>
       <c r="AE12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF12" s="3">
         <v>0</v>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,13 +1338,16 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1338,32 +1358,32 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>10</v>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>10</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>10</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>10</v>
@@ -1380,23 +1400,23 @@
       <c r="U14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>10</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>10</v>
@@ -1404,14 +1424,14 @@
       <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD14" s="3">
-        <v>200</v>
+      <c r="AD14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AF14" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AG14" s="3">
         <v>200</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,14 +1489,14 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S15" s="3">
-        <v>100</v>
-      </c>
       <c r="T15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1503,22 +1526,25 @@
         <v>0</v>
       </c>
       <c r="AD15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,16 +1576,17 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="E17" s="3">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="F17" s="3">
         <v>600</v>
@@ -1568,13 +1595,13 @@
         <v>600</v>
       </c>
       <c r="H17" s="3">
+        <v>600</v>
+      </c>
+      <c r="I17" s="3">
         <v>400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>400</v>
       </c>
       <c r="K17" s="3">
         <v>400</v>
@@ -1583,31 +1610,31 @@
         <v>400</v>
       </c>
       <c r="M17" s="3">
+        <v>400</v>
+      </c>
+      <c r="N17" s="3">
         <v>500</v>
       </c>
-      <c r="N17" s="3">
-        <v>200</v>
-      </c>
       <c r="O17" s="3">
+        <v>200</v>
+      </c>
+      <c r="P17" s="3">
         <v>300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="R17" s="3">
-        <v>200</v>
-      </c>
       <c r="S17" s="3">
+        <v>200</v>
+      </c>
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>500</v>
-      </c>
-      <c r="U17" s="3">
-        <v>400</v>
       </c>
       <c r="V17" s="3">
         <v>400</v>
@@ -1619,13 +1646,13 @@
         <v>400</v>
       </c>
       <c r="Y17" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z17" s="3">
         <v>300</v>
       </c>
-      <c r="Z17" s="3">
-        <v>200</v>
-      </c>
       <c r="AA17" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AB17" s="3">
         <v>300</v>
@@ -1634,30 +1661,33 @@
         <v>300</v>
       </c>
       <c r="AD17" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE17" s="3">
         <v>1200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="3">
         <v>0</v>
@@ -1666,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3">
         <v>100</v>
@@ -1681,25 +1711,25 @@
         <v>100</v>
       </c>
       <c r="M18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N18" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O18" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R18" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S18" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T18" s="3">
         <v>0</v>
@@ -1708,13 +1738,13 @@
         <v>0</v>
       </c>
       <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
       <c r="X18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="3">
         <v>-100</v>
@@ -1732,22 +1762,25 @@
         <v>-100</v>
       </c>
       <c r="AD18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1842,11 +1876,11 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1854,11 +1888,11 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -1878,18 +1912,21 @@
         <v>0</v>
       </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
@@ -1898,40 +1935,40 @@
         <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M21" s="3">
         <v>100</v>
       </c>
       <c r="N21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P21" s="3">
         <v>100</v>
       </c>
       <c r="Q21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21" s="3">
         <v>0</v>
       </c>
       <c r="S21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T21" s="3">
         <v>100</v>
@@ -1940,13 +1977,13 @@
         <v>100</v>
       </c>
       <c r="V21" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W21" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="3">
         <v>-100</v>
@@ -1964,22 +2001,25 @@
         <v>-100</v>
       </c>
       <c r="AD21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-600</v>
-      </c>
-      <c r="AG21" s="3">
-        <v>-400</v>
       </c>
       <c r="AH21" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2001,8 +2041,8 @@
       <c r="I22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2013,8 +2053,8 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>10</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>10</v>
@@ -2052,8 +2092,8 @@
       <c r="Z22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -2076,16 +2116,19 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="3">
         <v>0</v>
@@ -2094,40 +2137,40 @@
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M23" s="3">
         <v>100</v>
       </c>
       <c r="N23" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O23" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P23" s="3">
         <v>100</v>
       </c>
       <c r="Q23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S23" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T23" s="3">
         <v>0</v>
@@ -2136,13 +2179,13 @@
         <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W23" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="3">
         <v>-100</v>
@@ -2160,22 +2203,25 @@
         <v>-100</v>
       </c>
       <c r="AD23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-600</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>-400</v>
       </c>
       <c r="AH23" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,16 +2419,19 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F26" s="3">
         <v>0</v>
@@ -2388,40 +2440,40 @@
         <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M26" s="3">
         <v>100</v>
       </c>
       <c r="N26" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O26" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P26" s="3">
         <v>100</v>
       </c>
       <c r="Q26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T26" s="3">
         <v>0</v>
@@ -2430,13 +2482,13 @@
         <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W26" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="3">
         <v>-100</v>
@@ -2454,72 +2506,75 @@
         <v>-100</v>
       </c>
       <c r="AD26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-600</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>-400</v>
       </c>
       <c r="AH26" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
         <v>-100</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K27" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N27" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O27" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P27" s="3">
         <v>100</v>
       </c>
       <c r="Q27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S27" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T27" s="3">
         <v>0</v>
@@ -2528,13 +2583,13 @@
         <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="W27" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="3">
         <v>-100</v>
@@ -2552,22 +2607,25 @@
         <v>-100</v>
       </c>
       <c r="AD27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-600</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>-400</v>
       </c>
       <c r="AH27" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2714,21 +2775,21 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>-100</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
@@ -2736,11 +2797,11 @@
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-100</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
         <v>0</v>
       </c>
@@ -2750,20 +2811,23 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
       <c r="AG29" s="3">
         <v>0</v>
       </c>
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3018,11 +3088,11 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -3030,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB32" s="3">
         <v>0</v>
@@ -3054,60 +3124,63 @@
         <v>0</v>
       </c>
       <c r="AH32" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
         <v>-100</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K33" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N33" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O33" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P33" s="3">
         <v>100</v>
       </c>
       <c r="Q33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S33" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T33" s="3">
         <v>0</v>
@@ -3116,22 +3189,22 @@
         <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>-100</v>
       </c>
       <c r="AB33" s="3">
         <v>-100</v>
@@ -3140,22 +3213,25 @@
         <v>-100</v>
       </c>
       <c r="AD33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-600</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>-400</v>
       </c>
       <c r="AH33" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,58 +3328,61 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
         <v>-100</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K35" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N35" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P35" s="3">
         <v>100</v>
       </c>
       <c r="Q35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S35" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T35" s="3">
         <v>0</v>
@@ -3312,22 +3391,22 @@
         <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>-100</v>
       </c>
       <c r="AB35" s="3">
         <v>-100</v>
@@ -3336,125 +3415,131 @@
         <v>-100</v>
       </c>
       <c r="AD35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-600</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>-400</v>
       </c>
       <c r="AH35" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,37 +3611,38 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>800</v>
+      </c>
+      <c r="E41" s="3">
         <v>700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>500</v>
-      </c>
-      <c r="G41" s="3">
-        <v>400</v>
       </c>
       <c r="H41" s="3">
         <v>400</v>
       </c>
       <c r="I41" s="3">
+        <v>400</v>
+      </c>
+      <c r="J41" s="3">
         <v>300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>500</v>
       </c>
-      <c r="K41" s="3">
-        <v>200</v>
-      </c>
       <c r="L41" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="M41" s="3">
         <v>400</v>
@@ -3564,11 +3651,11 @@
         <v>400</v>
       </c>
       <c r="O41" s="3">
+        <v>400</v>
+      </c>
+      <c r="P41" s="3">
         <v>300</v>
       </c>
-      <c r="P41" s="3">
-        <v>100</v>
-      </c>
       <c r="Q41" s="3">
         <v>100</v>
       </c>
@@ -3582,7 +3669,7 @@
         <v>100</v>
       </c>
       <c r="U41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V41" s="3">
         <v>0</v>
@@ -3612,19 +3699,22 @@
         <v>0</v>
       </c>
       <c r="AE41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF41" s="3">
         <v>100</v>
       </c>
       <c r="AG41" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AH41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,37 +3811,40 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
         <v>600</v>
-      </c>
-      <c r="E43" s="3">
-        <v>500</v>
       </c>
       <c r="F43" s="3">
         <v>500</v>
       </c>
       <c r="G43" s="3">
+        <v>500</v>
+      </c>
+      <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>600</v>
-      </c>
-      <c r="J43" s="3">
-        <v>500</v>
       </c>
       <c r="K43" s="3">
         <v>500</v>
       </c>
       <c r="L43" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="M43" s="3">
         <v>300</v>
@@ -3760,7 +3853,7 @@
         <v>300</v>
       </c>
       <c r="O43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P43" s="3">
         <v>200</v>
@@ -3775,10 +3868,10 @@
         <v>200</v>
       </c>
       <c r="T43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V43" s="3">
         <v>200</v>
@@ -3787,7 +3880,7 @@
         <v>200</v>
       </c>
       <c r="X43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y43" s="3">
         <v>100</v>
@@ -3796,10 +3889,10 @@
         <v>100</v>
       </c>
       <c r="AA43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB43" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC43" s="3">
         <v>100</v>
@@ -3814,18 +3907,21 @@
         <v>100</v>
       </c>
       <c r="AG43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E44" s="3">
         <v>0</v>
@@ -3876,10 +3972,10 @@
         <v>0</v>
       </c>
       <c r="U44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3935,16 +4034,16 @@
         <v>100</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
         <v>0</v>
       </c>
       <c r="J45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -3956,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="O45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P45" s="3">
         <v>100</v>
@@ -3965,19 +4064,19 @@
         <v>100</v>
       </c>
       <c r="R45" s="3">
-        <v>0</v>
-      </c>
-      <c r="S45" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
       <c r="U45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
@@ -3986,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="Y45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA45" s="3">
         <v>0</v>
@@ -4015,8 +4114,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4024,25 +4126,25 @@
         <v>1400</v>
       </c>
       <c r="E46" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F46" s="3">
         <v>1500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1100</v>
-      </c>
-      <c r="K46" s="3">
-        <v>700</v>
       </c>
       <c r="L46" s="3">
         <v>700</v>
@@ -4051,34 +4153,34 @@
         <v>700</v>
       </c>
       <c r="N46" s="3">
+        <v>700</v>
+      </c>
+      <c r="O46" s="3">
         <v>800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>600</v>
-      </c>
-      <c r="P46" s="3">
-        <v>300</v>
       </c>
       <c r="Q46" s="3">
         <v>300</v>
       </c>
       <c r="R46" s="3">
+        <v>300</v>
+      </c>
+      <c r="S46" s="3">
         <v>400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>300</v>
       </c>
-      <c r="T46" s="3">
-        <v>200</v>
-      </c>
       <c r="U46" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V46" s="3">
         <v>300</v>
       </c>
       <c r="W46" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X46" s="3">
         <v>200</v>
@@ -4087,19 +4189,19 @@
         <v>200</v>
       </c>
       <c r="Z46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA46" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC46" s="3">
         <v>100</v>
       </c>
       <c r="AD46" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE46" s="3">
         <v>200</v>
@@ -4111,22 +4213,25 @@
         <v>200</v>
       </c>
       <c r="AH46" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AI46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
         <v>100</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="3">
+        <v>100</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="3">
-        <v>100</v>
-      </c>
       <c r="G47" s="3">
         <v>100</v>
       </c>
@@ -4149,7 +4254,7 @@
         <v>100</v>
       </c>
       <c r="N47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -4166,8 +4271,8 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>10</v>
+      <c r="T47" s="3">
+        <v>0</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>10</v>
@@ -4184,8 +4289,8 @@
       <c r="Y47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -4211,13 +4316,16 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E48" s="3">
         <v>0</v>
@@ -4226,13 +4334,13 @@
         <v>0</v>
       </c>
       <c r="G48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3">
         <v>100</v>
       </c>
       <c r="I48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J48" s="3">
         <v>0</v>
@@ -4264,8 +4372,8 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>10</v>
+      <c r="T48" s="3">
+        <v>0</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>10</v>
@@ -4282,8 +4390,8 @@
       <c r="Y48" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z48" s="3">
-        <v>0</v>
+      <c r="Z48" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
@@ -4309,22 +4417,25 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>10</v>
+        <v>100</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>10</v>
@@ -4338,8 +4449,8 @@
       <c r="K49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -4356,21 +4467,21 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-      <c r="R49" s="3" t="s">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="S49" s="3">
-        <v>500</v>
       </c>
       <c r="T49" s="3">
         <v>500</v>
       </c>
       <c r="U49" s="3">
+        <v>500</v>
+      </c>
+      <c r="V49" s="3">
         <v>600</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
-      </c>
       <c r="W49" s="3">
         <v>0</v>
       </c>
@@ -4378,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="Y49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="3">
         <v>100</v>
@@ -4390,7 +4501,7 @@
         <v>100</v>
       </c>
       <c r="AC49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD49" s="3">
         <v>200</v>
@@ -4399,16 +4510,19 @@
         <v>200</v>
       </c>
       <c r="AF49" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG49" s="3">
         <v>300</v>
       </c>
-      <c r="AG49" s="3">
-        <v>200</v>
-      </c>
       <c r="AH49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4696,13 +4816,16 @@
         <v>0</v>
       </c>
       <c r="AG52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,34 +4922,37 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1600</v>
-      </c>
-      <c r="F54" s="3">
-        <v>1300</v>
       </c>
       <c r="G54" s="3">
         <v>1300</v>
       </c>
       <c r="H54" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I54" s="3">
         <v>1100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1100</v>
-      </c>
-      <c r="K54" s="3">
-        <v>800</v>
       </c>
       <c r="L54" s="3">
         <v>800</v>
@@ -4838,52 +4964,52 @@
         <v>800</v>
       </c>
       <c r="O54" s="3">
+        <v>800</v>
+      </c>
+      <c r="P54" s="3">
         <v>700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>400</v>
-      </c>
-      <c r="S54" s="3">
-        <v>800</v>
       </c>
       <c r="T54" s="3">
         <v>800</v>
       </c>
       <c r="U54" s="3">
+        <v>800</v>
+      </c>
+      <c r="V54" s="3">
         <v>900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>300</v>
       </c>
-      <c r="W54" s="3">
-        <v>200</v>
-      </c>
       <c r="X54" s="3">
         <v>200</v>
       </c>
       <c r="Y54" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z54" s="3">
         <v>300</v>
       </c>
-      <c r="Z54" s="3">
-        <v>200</v>
-      </c>
       <c r="AA54" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB54" s="3">
         <v>400</v>
-      </c>
-      <c r="AB54" s="3">
-        <v>300</v>
       </c>
       <c r="AC54" s="3">
         <v>300</v>
       </c>
       <c r="AD54" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AE54" s="3">
         <v>400</v>
@@ -4892,13 +5018,16 @@
         <v>400</v>
       </c>
       <c r="AG54" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH54" s="3">
         <v>500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,19 +5099,20 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
       </c>
       <c r="F57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G57" s="3">
         <v>100</v>
@@ -4999,7 +5130,7 @@
         <v>100</v>
       </c>
       <c r="L57" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M57" s="3">
         <v>200</v>
@@ -5017,22 +5148,22 @@
         <v>200</v>
       </c>
       <c r="R57" s="3">
+        <v>200</v>
+      </c>
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
-        <v>200</v>
-      </c>
       <c r="T57" s="3">
         <v>200</v>
       </c>
       <c r="U57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V57" s="3">
         <v>300</v>
       </c>
       <c r="W57" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="X57" s="3">
         <v>500</v>
@@ -5056,7 +5187,7 @@
         <v>500</v>
       </c>
       <c r="AE57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AF57" s="3">
         <v>400</v>
@@ -5067,8 +5198,11 @@
       <c r="AH57" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5115,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S58" s="3">
         <v>100</v>
@@ -5148,13 +5282,13 @@
         <v>100</v>
       </c>
       <c r="AC58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AE58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF58" s="3">
         <v>100</v>
@@ -5163,10 +5297,13 @@
         <v>100</v>
       </c>
       <c r="AH58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5177,37 +5314,37 @@
         <v>1500</v>
       </c>
       <c r="F59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G59" s="3">
         <v>1100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
-      </c>
-      <c r="L59" s="3">
-        <v>800</v>
       </c>
       <c r="M59" s="3">
         <v>800</v>
       </c>
       <c r="N59" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="O59" s="3">
         <v>1000</v>
       </c>
       <c r="P59" s="3">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="Q59" s="3">
         <v>700</v>
@@ -5219,16 +5356,16 @@
         <v>700</v>
       </c>
       <c r="T59" s="3">
+        <v>700</v>
+      </c>
+      <c r="U59" s="3">
         <v>800</v>
-      </c>
-      <c r="U59" s="3">
-        <v>1000</v>
       </c>
       <c r="V59" s="3">
         <v>1000</v>
       </c>
       <c r="W59" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="X59" s="3">
         <v>800</v>
@@ -5237,13 +5374,13 @@
         <v>800</v>
       </c>
       <c r="Z59" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="AA59" s="3">
         <v>600</v>
       </c>
       <c r="AB59" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AC59" s="3">
         <v>400</v>
@@ -5255,16 +5392,19 @@
         <v>400</v>
       </c>
       <c r="AF59" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AG59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AH59" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5272,97 +5412,100 @@
         <v>1600</v>
       </c>
       <c r="E60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F60" s="3">
         <v>1500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1100</v>
-      </c>
-      <c r="H60" s="3">
-        <v>900</v>
       </c>
       <c r="I60" s="3">
         <v>900</v>
       </c>
       <c r="J60" s="3">
+        <v>900</v>
+      </c>
+      <c r="K60" s="3">
         <v>1100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1200</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>1000</v>
       </c>
       <c r="AC60" s="3">
         <v>1000</v>
       </c>
       <c r="AD60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE60" s="3">
         <v>800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5400,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>100</v>
@@ -5415,7 +5558,7 @@
         <v>100</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -5445,10 +5588,10 @@
         <v>0</v>
       </c>
       <c r="AD61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF61" s="3">
         <v>0</v>
@@ -5457,15 +5600,18 @@
         <v>0</v>
       </c>
       <c r="AH61" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E62" s="3">
         <v>100</v>
@@ -5495,10 +5641,10 @@
         <v>100</v>
       </c>
       <c r="N62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O62" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -5516,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="U62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V62" s="3">
         <v>100</v>
@@ -5528,10 +5674,10 @@
         <v>100</v>
       </c>
       <c r="Y62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA62" s="3">
         <v>100</v>
@@ -5552,13 +5698,16 @@
         <v>100</v>
       </c>
       <c r="AG62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,8 +6006,11 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5863,52 +6021,52 @@
         <v>1600</v>
       </c>
       <c r="F66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G66" s="3">
         <v>1300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1200</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1000</v>
       </c>
       <c r="I66" s="3">
         <v>1000</v>
       </c>
       <c r="J66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K66" s="3">
         <v>1200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>900</v>
-      </c>
-      <c r="L66" s="3">
-        <v>1100</v>
       </c>
       <c r="M66" s="3">
         <v>1100</v>
       </c>
       <c r="N66" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="O66" s="3">
         <v>1300</v>
       </c>
       <c r="P66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q66" s="3">
         <v>1000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1200</v>
-      </c>
-      <c r="S66" s="3">
-        <v>1100</v>
       </c>
       <c r="T66" s="3">
         <v>1100</v>
       </c>
       <c r="U66" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="V66" s="3">
         <v>1500</v>
@@ -5917,40 +6075,43 @@
         <v>1500</v>
       </c>
       <c r="X66" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y66" s="3">
         <v>1600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1500</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>1400</v>
       </c>
       <c r="AA66" s="3">
         <v>1400</v>
       </c>
       <c r="AB66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AC66" s="3">
         <v>1200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1100</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>1000</v>
       </c>
       <c r="AE66" s="3">
         <v>1000</v>
       </c>
       <c r="AF66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG66" s="3">
         <v>800</v>
-      </c>
-      <c r="AG66" s="3">
-        <v>700</v>
       </c>
       <c r="AH66" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,8 +6548,11 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6398,85 +6572,88 @@
         <v>-15200</v>
       </c>
       <c r="I72" s="3">
-        <v>-15300</v>
+        <v>-15200</v>
       </c>
       <c r="J72" s="3">
         <v>-15300</v>
       </c>
       <c r="K72" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="L72" s="3">
         <v>-15400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-15500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-15600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-15700</v>
-      </c>
-      <c r="O72" s="3">
-        <v>-15900</v>
       </c>
       <c r="P72" s="3">
         <v>-15900</v>
       </c>
       <c r="Q72" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="R72" s="3">
         <v>-16000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-16100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-16200</v>
-      </c>
-      <c r="T72" s="3">
-        <v>-16300</v>
       </c>
       <c r="U72" s="3">
         <v>-16300</v>
       </c>
       <c r="V72" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="W72" s="3">
         <v>-16200</v>
-      </c>
-      <c r="W72" s="3">
-        <v>-16300</v>
       </c>
       <c r="X72" s="3">
         <v>-16300</v>
       </c>
       <c r="Y72" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-16200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-15900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-15700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-15600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-15500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-15400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-15300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-15000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-14700</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,8 +6952,11 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -6793,82 +6979,85 @@
         <v>0</v>
       </c>
       <c r="J76" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K76" s="3">
         <v>-100</v>
       </c>
       <c r="L76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M76" s="3">
         <v>-300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-700</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>-800</v>
       </c>
       <c r="R76" s="3">
         <v>-800</v>
       </c>
       <c r="S76" s="3">
-        <v>-400</v>
+        <v>-800</v>
       </c>
       <c r="T76" s="3">
         <v>-400</v>
       </c>
       <c r="U76" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V76" s="3">
         <v>-600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-1200</v>
-      </c>
-      <c r="W76" s="3">
-        <v>-1300</v>
       </c>
       <c r="X76" s="3">
         <v>-1300</v>
       </c>
       <c r="Y76" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="Z76" s="3">
         <v>-1200</v>
       </c>
       <c r="AA76" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="AB76" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,161 +7154,167 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
         <v>-100</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K81" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N81" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O81" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P81" s="3">
         <v>100</v>
       </c>
       <c r="Q81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R81" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S81" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T81" s="3">
         <v>0</v>
@@ -7128,22 +7323,22 @@
         <v>0</v>
       </c>
       <c r="V81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>-100</v>
       </c>
       <c r="AB81" s="3">
         <v>-100</v>
@@ -7152,22 +7347,25 @@
         <v>-100</v>
       </c>
       <c r="AD81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-600</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>-400</v>
       </c>
       <c r="AH81" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7250,13 +7449,13 @@
         <v>0</v>
       </c>
       <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
         <v>-100</v>
       </c>
-      <c r="S83" s="3">
-        <v>100</v>
-      </c>
       <c r="T83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -7286,10 +7485,10 @@
         <v>0</v>
       </c>
       <c r="AD83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF83" s="3">
         <v>0</v>
@@ -7297,11 +7496,14 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-      <c r="AH83" s="3" t="s">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>300</v>
+      </c>
+      <c r="F89" s="3">
+        <v>400</v>
+      </c>
+      <c r="G89" s="3">
+        <v>100</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>100</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K89" s="3">
+        <v>200</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
+        <v>100</v>
+      </c>
+      <c r="P89" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>100</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
-        <v>400</v>
-      </c>
-      <c r="F89" s="3">
-        <v>100</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>100</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="U89" s="3">
+        <v>200</v>
+      </c>
+      <c r="V89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
-        <v>200</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-200</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3">
-        <v>100</v>
-      </c>
-      <c r="O89" s="3">
-        <v>200</v>
-      </c>
-      <c r="P89" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T89" s="3">
-        <v>200</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AG89" s="3">
-        <v>0</v>
-      </c>
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,19 +8144,20 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -7962,8 +8183,8 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>10</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>10</v>
@@ -7971,14 +8192,14 @@
       <c r="Q91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
+      <c r="R91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,19 +8445,22 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
@@ -8256,8 +8486,8 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>10</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>10</v>
@@ -8265,8 +8495,8 @@
       <c r="Q94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -8289,26 +8519,26 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-      <c r="Z94" s="3" t="s">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>10</v>
+      <c r="AD94" s="3">
+        <v>0</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
+      <c r="AF94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AG94" s="3">
         <v>0</v>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,8 +8987,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8795,16 +9041,16 @@
         <v>0</v>
       </c>
       <c r="S100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>100</v>
+      </c>
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
-        <v>100</v>
-      </c>
       <c r="V100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -8813,37 +9059,40 @@
         <v>0</v>
       </c>
       <c r="Y100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="AA100" s="3">
-        <v>100</v>
-      </c>
       <c r="AB100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>300</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AG100" s="3">
         <v>200</v>
       </c>
       <c r="AH100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,49 +9189,52 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="E102" s="3">
+        <v>200</v>
+      </c>
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
-        <v>100</v>
-      </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
+        <v>100</v>
+      </c>
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
-        <v>200</v>
-      </c>
       <c r="K102" s="3">
+        <v>200</v>
+      </c>
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
       <c r="N102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O102" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q102" s="3">
         <v>0</v>
@@ -8994,10 +9246,10 @@
         <v>0</v>
       </c>
       <c r="T102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V102" s="3">
         <v>0</v>
@@ -9030,12 +9282,15 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG102" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AH102" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
